--- a/9984.T_settings.xlsx
+++ b/9984.T_settings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>AverageProfit</t>
+          <t>ProfitPerTrade</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -464,12 +464,27 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>FinalCapital</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>TotalCommission</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>AverageHoldDays</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>MaxDrawdown</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Eligible</t>
         </is>
       </c>
     </row>
@@ -482,7 +497,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -491,33 +506,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>97.08234466672275</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.412833848487398</v>
+      </c>
+      <c r="I2" t="n">
+        <v>970823.4466672274</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1970823.446667227</v>
+      </c>
+      <c r="K2" t="n">
+        <v>56366.99139672238</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5.636363636363637</v>
+      </c>
+      <c r="M2" t="n">
+        <v>17.43472530400954</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -538,33 +554,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>86.70360734698583</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.10021219688152</v>
+      </c>
+      <c r="I3" t="n">
+        <v>867036.0734698584</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1867036.073469858</v>
+      </c>
+      <c r="K3" t="n">
+        <v>43326.29027495484</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.411764705882353</v>
+      </c>
+      <c r="M3" t="n">
+        <v>9.110615924121603</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -576,7 +593,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -585,33 +602,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>86.70360734698583</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.10021219688152</v>
+      </c>
+      <c r="I4" t="n">
+        <v>867036.0734698584</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1867036.073469858</v>
+      </c>
+      <c r="K4" t="n">
+        <v>43326.29027495484</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5.411764705882353</v>
+      </c>
+      <c r="M4" t="n">
+        <v>9.110615924121603</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -619,46 +637,47 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>86.70360734698583</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5.10021219688152</v>
+      </c>
+      <c r="I5" t="n">
+        <v>867036.0734698584</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1867036.073469858</v>
+      </c>
+      <c r="K5" t="n">
+        <v>43326.29027495484</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.411764705882353</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9.110615924121603</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -666,46 +685,47 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>82.23134730257878</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.568408183476599</v>
+      </c>
+      <c r="I6" t="n">
+        <v>822313.4730257879</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1822313.473025788</v>
+      </c>
+      <c r="K6" t="n">
+        <v>44247.8290646036</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5.777777777777778</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9.861897909029588</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -713,11 +733,11 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -726,33 +746,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>82.23134730257878</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.568408183476599</v>
+      </c>
+      <c r="I7" t="n">
+        <v>822313.4730257879</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1822313.473025788</v>
+      </c>
+      <c r="K7" t="n">
+        <v>44247.8290646036</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5.777777777777778</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9.861897909029588</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -764,42 +785,43 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>81.03653641052605</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5.402435760701737</v>
+      </c>
+      <c r="I8" t="n">
+        <v>810365.3641052605</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1810365.36410526</v>
+      </c>
+      <c r="K8" t="n">
+        <v>38249.26677964552</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5.266666666666667</v>
+      </c>
+      <c r="M8" t="n">
+        <v>8.783280702976766</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -807,46 +829,47 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>81.03653641052605</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.402435760701737</v>
+      </c>
+      <c r="I9" t="n">
+        <v>810365.3641052605</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1810365.36410526</v>
+      </c>
+      <c r="K9" t="n">
+        <v>38249.26677964552</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.266666666666667</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8.783280702976766</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -854,7 +877,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -867,33 +890,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>81.03653641052605</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.402435760701737</v>
+      </c>
+      <c r="I10" t="n">
+        <v>810365.3641052605</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1810365.36410526</v>
+      </c>
+      <c r="K10" t="n">
+        <v>38249.26677964552</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.266666666666667</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8.783280702976766</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -905,42 +929,43 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>54.54545454545454</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>73.19692288381781</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.327132858355355</v>
+      </c>
+      <c r="I11" t="n">
+        <v>731969.2288381781</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1731969.228838178</v>
+      </c>
+      <c r="K11" t="n">
+        <v>50352.77841280588</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.272727272727272</v>
+      </c>
+      <c r="M11" t="n">
+        <v>17.43472530400955</v>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -948,46 +973,47 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>54.54545454545454</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>71.55984134044672</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.252720060929397</v>
+      </c>
+      <c r="I12" t="n">
+        <v>715598.4134044673</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1715598.413404467</v>
+      </c>
+      <c r="K12" t="n">
+        <v>49940.57061662957</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5.318181818181818</v>
+      </c>
+      <c r="M12" t="n">
+        <v>17.43472530400955</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -995,46 +1021,47 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>60.14545029242448</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.341413905134694</v>
+      </c>
+      <c r="I13" t="n">
+        <v>601454.5029242449</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1601454.502924245</v>
+      </c>
+      <c r="K13" t="n">
+        <v>39461.89747317667</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="M13" t="n">
+        <v>19.41862913259938</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1046,42 +1073,43 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>60.14545029242448</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.341413905134694</v>
+      </c>
+      <c r="I14" t="n">
+        <v>601454.5029242449</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1601454.502924245</v>
+      </c>
+      <c r="K14" t="n">
+        <v>39461.89747317667</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="M14" t="n">
+        <v>19.41862913259938</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1089,46 +1117,47 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>58.63170627346831</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.257317015192684</v>
+      </c>
+      <c r="I15" t="n">
+        <v>586317.062734683</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1586317.062734683</v>
+      </c>
+      <c r="K15" t="n">
+        <v>39133.87478438458</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.388888888888889</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20.18030901777307</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1136,46 +1165,47 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>58.63170627346831</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.257317015192684</v>
+      </c>
+      <c r="I16" t="n">
+        <v>586317.062734683</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1586317.062734683</v>
+      </c>
+      <c r="K16" t="n">
+        <v>39133.87478438458</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5.388888888888889</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20.18030901777307</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1187,42 +1217,43 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>23.75528123084796</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.159571020986178</v>
+      </c>
+      <c r="I17" t="n">
+        <v>237552.8123084796</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1237552.81230848</v>
+      </c>
+      <c r="K17" t="n">
+        <v>21200.18926792442</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5.818181818181818</v>
+      </c>
+      <c r="M17" t="n">
+        <v>18.06337496523121</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1230,46 +1261,47 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>23.75528123084796</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.159571020986178</v>
+      </c>
+      <c r="I18" t="n">
+        <v>237552.8123084796</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1237552.81230848</v>
+      </c>
+      <c r="K18" t="n">
+        <v>21200.18926792442</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5.818181818181818</v>
+      </c>
+      <c r="M18" t="n">
+        <v>18.06337496523121</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1277,11 +1309,11 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1290,33 +1322,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>23.75528123084796</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.159571020986178</v>
+      </c>
+      <c r="I19" t="n">
+        <v>237552.8123084796</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1237552.81230848</v>
+      </c>
+      <c r="K19" t="n">
+        <v>21200.18926792442</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5.818181818181818</v>
+      </c>
+      <c r="M19" t="n">
+        <v>18.06337496523121</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1328,42 +1361,43 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.32956152758133</v>
+        <v>20.34523346371006</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-1.33%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-13,296円</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>14日</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.034523346371006</v>
+      </c>
+      <c r="I20" t="n">
+        <v>203452.3346371006</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1203452.334637101</v>
+      </c>
+      <c r="K20" t="n">
+        <v>18860.65492349565</v>
+      </c>
+      <c r="L20" t="n">
+        <v>6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20.32111946282102</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1371,46 +1405,47 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.32956152758133</v>
+        <v>20.34523346371006</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-1.33%</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-13,296円</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>14日</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.034523346371006</v>
+      </c>
+      <c r="I21" t="n">
+        <v>203452.3346371006</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1203452.334637101</v>
+      </c>
+      <c r="K21" t="n">
+        <v>18860.65492349565</v>
+      </c>
+      <c r="L21" t="n">
+        <v>6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20.32111946282102</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1418,46 +1453,47 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>41.66666666666667</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.32956152758133</v>
+        <v>17.14019683743864</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-1.33%</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-13,296円</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>14日</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.42834973645322</v>
+      </c>
+      <c r="I22" t="n">
+        <v>171401.9683743864</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1171401.968374386</v>
+      </c>
+      <c r="K22" t="n">
+        <v>21964.92599062613</v>
+      </c>
+      <c r="L22" t="n">
+        <v>6.166666666666667</v>
+      </c>
+      <c r="M22" t="n">
+        <v>22.44312897754746</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1465,46 +1501,47 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>41.66666666666667</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.32956152758133</v>
+        <v>17.14019683743864</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-1.33%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-13,296円</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>14日</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.42834973645322</v>
+      </c>
+      <c r="I23" t="n">
+        <v>171401.9683743864</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1171401.968374386</v>
+      </c>
+      <c r="K23" t="n">
+        <v>21964.92599062613</v>
+      </c>
+      <c r="L23" t="n">
+        <v>6.166666666666667</v>
+      </c>
+      <c r="M23" t="n">
+        <v>22.44312897754746</v>
+      </c>
+      <c r="N23" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1512,46 +1549,47 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.32956152758133</v>
+        <v>16.495973625494</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>-1.33%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>-13,296円</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>14日</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.6495973625494</v>
+      </c>
+      <c r="I24" t="n">
+        <v>164959.73625494</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1164959.73625494</v>
+      </c>
+      <c r="K24" t="n">
+        <v>18409.61063794609</v>
+      </c>
+      <c r="L24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M24" t="n">
+        <v>22.86966007368175</v>
+      </c>
+      <c r="N24" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1563,42 +1601,43 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.32956152758133</v>
+        <v>16.495973625494</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>-1.33%</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>-13,296円</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>14日</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.6495973625494</v>
+      </c>
+      <c r="I25" t="n">
+        <v>164959.73625494</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1164959.73625494</v>
+      </c>
+      <c r="K25" t="n">
+        <v>18409.61063794609</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M25" t="n">
+        <v>22.86966007368175</v>
+      </c>
+      <c r="N25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1606,7 +1645,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1615,37 +1654,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.32956152758133</v>
+        <v>16.495973625494</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-1.33%</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>-13,296円</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>14日</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.6495973625494</v>
+      </c>
+      <c r="I26" t="n">
+        <v>164959.73625494</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1164959.73625494</v>
+      </c>
+      <c r="K26" t="n">
+        <v>18409.61063794609</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M26" t="n">
+        <v>22.86966007368175</v>
+      </c>
+      <c r="N26" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1657,42 +1697,43 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.32956152758133</v>
+        <v>16.4565122289249</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>-1.33%</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>-13,296円</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>14日</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.64565122289249</v>
+      </c>
+      <c r="I27" t="n">
+        <v>164565.122289249</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1164565.122289249</v>
+      </c>
+      <c r="K27" t="n">
+        <v>18404.98667433481</v>
+      </c>
+      <c r="L27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M27" t="n">
+        <v>22.89578690739641</v>
+      </c>
+      <c r="N27" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1700,46 +1741,47 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>38.46153846153847</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.32956152758133</v>
+        <v>16.12986652932521</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-1.33%</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>-13,296円</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>14日</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.240758963794247</v>
+      </c>
+      <c r="I28" t="n">
+        <v>161298.6652932521</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1161298.665293252</v>
+      </c>
+      <c r="K28" t="n">
+        <v>23858.97238095295</v>
+      </c>
+      <c r="L28" t="n">
+        <v>4.538461538461538</v>
+      </c>
+      <c r="M28" t="n">
+        <v>23.11205441486057</v>
+      </c>
+      <c r="N28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1747,7 +1789,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1760,33 +1802,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>38.46153846153847</v>
       </c>
       <c r="F29" t="n">
-        <v>-4.07040704070407</v>
+        <v>16.12986652932521</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>-4.07%</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>-40,704円</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.240758963794247</v>
+      </c>
+      <c r="I29" t="n">
+        <v>161298.6652932521</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1161298.665293252</v>
+      </c>
+      <c r="K29" t="n">
+        <v>23858.97238095295</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4.538461538461538</v>
+      </c>
+      <c r="M29" t="n">
+        <v>23.11205441486057</v>
+      </c>
+      <c r="N29" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1794,46 +1837,47 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>38.46153846153847</v>
       </c>
       <c r="F30" t="n">
-        <v>-4.07040704070407</v>
+        <v>16.12986652932521</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>-4.07%</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>-40,704円</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.240758963794247</v>
+      </c>
+      <c r="I30" t="n">
+        <v>161298.6652932521</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1161298.665293252</v>
+      </c>
+      <c r="K30" t="n">
+        <v>23858.97238095295</v>
+      </c>
+      <c r="L30" t="n">
+        <v>4.538461538461538</v>
+      </c>
+      <c r="M30" t="n">
+        <v>23.11205441486057</v>
+      </c>
+      <c r="N30" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1845,7 +1889,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1854,33 +1898,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>41.66666666666667</v>
       </c>
       <c r="F31" t="n">
-        <v>-4.07040704070407</v>
+        <v>13.35504010311707</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>-4.07%</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>-40,704円</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.112920008593089</v>
+      </c>
+      <c r="I31" t="n">
+        <v>133550.4010311707</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1133550.401031171</v>
+      </c>
+      <c r="K31" t="n">
+        <v>21405.91909900709</v>
+      </c>
+      <c r="L31" t="n">
+        <v>7.333333333333333</v>
+      </c>
+      <c r="M31" t="n">
+        <v>24.94922782806363</v>
+      </c>
+      <c r="N31" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1888,11 +1933,11 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1901,33 +1946,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F32" t="n">
-        <v>-4.07040704070407</v>
+        <v>-9.380418605275139</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>-4.07%</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>-40,704円</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.9380418605275139</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-93804.18605275138</v>
+      </c>
+      <c r="J32" t="n">
+        <v>906195.8139472486</v>
+      </c>
+      <c r="K32" t="n">
+        <v>18087.70385511089</v>
+      </c>
+      <c r="L32" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="M32" t="n">
+        <v>23.00449062451491</v>
+      </c>
+      <c r="N32" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1935,7 +1981,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1948,33 +1994,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F33" t="n">
-        <v>-4.07040704070407</v>
+        <v>-9.380418605275139</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-4.07%</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>-40,704円</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.9380418605275139</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-93804.18605275138</v>
+      </c>
+      <c r="J33" t="n">
+        <v>906195.8139472486</v>
+      </c>
+      <c r="K33" t="n">
+        <v>18087.70385511089</v>
+      </c>
+      <c r="L33" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="M33" t="n">
+        <v>23.00449062451491</v>
+      </c>
+      <c r="N33" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1982,7 +2029,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1991,37 +2038,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F34" t="n">
-        <v>-4.07040704070407</v>
+        <v>-9.380418605275139</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-4.07%</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>-40,704円</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.9380418605275139</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-93804.18605275138</v>
+      </c>
+      <c r="J34" t="n">
+        <v>906195.8139472486</v>
+      </c>
+      <c r="K34" t="n">
+        <v>18087.70385511089</v>
+      </c>
+      <c r="L34" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="M34" t="n">
+        <v>23.00449062451491</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2029,11 +2077,11 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2042,33 +2090,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="F35" t="n">
-        <v>-4.07040704070407</v>
+        <v>-10.33621768878931</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>-4.07%</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>-40,704円</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-1.148468632087701</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-103362.1768878931</v>
+      </c>
+      <c r="J35" t="n">
+        <v>896637.8231121069</v>
+      </c>
+      <c r="K35" t="n">
+        <v>15810.27362680338</v>
+      </c>
+      <c r="L35" t="n">
+        <v>11.22222222222222</v>
+      </c>
+      <c r="M35" t="n">
+        <v>23.36338005122904</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2076,46 +2125,47 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="F36" t="n">
-        <v>-4.07040704070407</v>
+        <v>-10.33621768878931</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-4.07%</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-40,704円</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-1.148468632087701</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-103362.1768878931</v>
+      </c>
+      <c r="J36" t="n">
+        <v>896637.8231121069</v>
+      </c>
+      <c r="K36" t="n">
+        <v>15810.27362680338</v>
+      </c>
+      <c r="L36" t="n">
+        <v>11.22222222222222</v>
+      </c>
+      <c r="M36" t="n">
+        <v>23.36338005122904</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2136,33 +2186,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F37" t="n">
-        <v>-4.07040704070407</v>
+        <v>-11.13645464472597</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>-4.07%</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>-40,704円</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-1.392056830590747</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-111364.5464472597</v>
+      </c>
+      <c r="J37" t="n">
+        <v>888635.4535527403</v>
+      </c>
+      <c r="K37" t="n">
+        <v>14045.16168299097</v>
+      </c>
+      <c r="L37" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="M37" t="n">
+        <v>24.0473513703088</v>
+      </c>
+      <c r="N37" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2170,46 +2221,47 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F38" t="n">
-        <v>-4.07040704070407</v>
+        <v>-11.13645464472597</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>-4.07%</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>-40,704円</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-1.392056830590747</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-111364.5464472597</v>
+      </c>
+      <c r="J38" t="n">
+        <v>888635.4535527403</v>
+      </c>
+      <c r="K38" t="n">
+        <v>14045.16168299097</v>
+      </c>
+      <c r="L38" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="M38" t="n">
+        <v>24.0473513703088</v>
+      </c>
+      <c r="N38" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2217,11 +2269,11 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2230,33 +2282,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F39" t="n">
-        <v>-4.07040704070407</v>
+        <v>-11.13645464472597</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>-4.07%</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>-40,704円</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-1.392056830590747</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-111364.5464472597</v>
+      </c>
+      <c r="J39" t="n">
+        <v>888635.4535527403</v>
+      </c>
+      <c r="K39" t="n">
+        <v>14045.16168299097</v>
+      </c>
+      <c r="L39" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="M39" t="n">
+        <v>24.0473513703088</v>
+      </c>
+      <c r="N39" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2264,46 +2317,47 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="F40" t="n">
-        <v>-4.07040704070407</v>
+        <v>-13.23352773779847</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>-4.07%</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>-40,704円</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-1.470391970866497</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-132335.2773779847</v>
+      </c>
+      <c r="J40" t="n">
+        <v>867664.7226220153</v>
+      </c>
+      <c r="K40" t="n">
+        <v>15450.5573568401</v>
+      </c>
+      <c r="L40" t="n">
+        <v>12.77777777777778</v>
+      </c>
+      <c r="M40" t="n">
+        <v>25.83974278516993</v>
+      </c>
+      <c r="N40" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2311,11 +2365,11 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2324,33 +2378,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.07040704070407</v>
+        <v>-18.35536665277703</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>-4.07%</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>-40,704円</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-2.294420831597129</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-183553.6665277703</v>
+      </c>
+      <c r="J41" t="n">
+        <v>816446.3334722297</v>
+      </c>
+      <c r="K41" t="n">
+        <v>13284.21522915587</v>
+      </c>
+      <c r="L41" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="M41" t="n">
+        <v>30.217434783525</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2358,46 +2413,47 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F42" t="n">
-        <v>-4.07040704070407</v>
+        <v>-18.35536665277703</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>-4.07%</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>-40,704円</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-2.294420831597129</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-183553.6665277703</v>
+      </c>
+      <c r="J42" t="n">
+        <v>816446.3334722297</v>
+      </c>
+      <c r="K42" t="n">
+        <v>13284.21522915587</v>
+      </c>
+      <c r="L42" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="M42" t="n">
+        <v>30.217434783525</v>
+      </c>
+      <c r="N42" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2405,11 +2461,11 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2418,33 +2474,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="F43" t="n">
-        <v>-4.07040704070407</v>
+        <v>-19.0250500073108</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>-4.07%</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>-40,704円</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-1.729550000664618</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-190250.500073108</v>
+      </c>
+      <c r="J43" t="n">
+        <v>809749.499926892</v>
+      </c>
+      <c r="K43" t="n">
+        <v>18083.65169675799</v>
+      </c>
+      <c r="L43" t="n">
+        <v>7.363636363636363</v>
+      </c>
+      <c r="M43" t="n">
+        <v>30.78982050498932</v>
+      </c>
+      <c r="N43" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2452,7 +2509,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2461,37 +2518,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="F44" t="n">
-        <v>-4.07040704070407</v>
+        <v>-19.0250500073108</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>-4.07%</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>-40,704円</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-1.729550000664618</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-190250.500073108</v>
+      </c>
+      <c r="J44" t="n">
+        <v>809749.499926892</v>
+      </c>
+      <c r="K44" t="n">
+        <v>18083.65169675799</v>
+      </c>
+      <c r="L44" t="n">
+        <v>7.363636363636363</v>
+      </c>
+      <c r="M44" t="n">
+        <v>30.78982050498932</v>
+      </c>
+      <c r="N44" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2512,33 +2570,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="F45" t="n">
-        <v>-4.07040704070407</v>
+        <v>-19.0250500073108</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>-4.07%</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>-40,704円</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-1.729550000664618</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-190250.500073108</v>
+      </c>
+      <c r="J45" t="n">
+        <v>809749.499926892</v>
+      </c>
+      <c r="K45" t="n">
+        <v>18083.65169675799</v>
+      </c>
+      <c r="L45" t="n">
+        <v>7.363636363636363</v>
+      </c>
+      <c r="M45" t="n">
+        <v>30.78982050498932</v>
+      </c>
+      <c r="N45" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2546,46 +2605,47 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F46" t="n">
-        <v>-4.07040704070407</v>
+        <v>-20.99355356110469</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>-4.07%</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>-40,704円</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-2.624194195138087</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-209935.5356110469</v>
+      </c>
+      <c r="J46" t="n">
+        <v>790064.4643889531</v>
+      </c>
+      <c r="K46" t="n">
+        <v>13006.12360396261</v>
+      </c>
+      <c r="L46" t="n">
+        <v>12</v>
+      </c>
+      <c r="M46" t="n">
+        <v>32.4723221219331</v>
+      </c>
+      <c r="N46" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/9984.T_settings.xlsx
+++ b/9984.T_settings.xlsx
@@ -509,28 +509,28 @@
         <v>59.09090909090909</v>
       </c>
       <c r="F2" t="n">
-        <v>97.08234466672275</v>
+        <v>97.08233534203404</v>
       </c>
       <c r="G2" t="n">
         <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>4.412833848487398</v>
+        <v>4.412833424637911</v>
       </c>
       <c r="I2" t="n">
-        <v>970823.4466672274</v>
+        <v>970823.3534203405</v>
       </c>
       <c r="J2" t="n">
-        <v>1970823.446667227</v>
+        <v>1970823.35342034</v>
       </c>
       <c r="K2" t="n">
-        <v>56366.99139672238</v>
+        <v>56366.98959484799</v>
       </c>
       <c r="L2" t="n">
         <v>5.636363636363637</v>
       </c>
       <c r="M2" t="n">
-        <v>17.43472530400954</v>
+        <v>17.43472003067039</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -557,28 +557,28 @@
         <v>64.70588235294117</v>
       </c>
       <c r="F3" t="n">
-        <v>86.70360734698583</v>
+        <v>86.70357713726115</v>
       </c>
       <c r="G3" t="n">
         <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>5.10021219688152</v>
+        <v>5.100210419838891</v>
       </c>
       <c r="I3" t="n">
-        <v>867036.0734698584</v>
+        <v>867035.7713726114</v>
       </c>
       <c r="J3" t="n">
-        <v>1867036.073469858</v>
+        <v>1867035.771372611</v>
       </c>
       <c r="K3" t="n">
-        <v>43326.29027495484</v>
+        <v>43326.28461176829</v>
       </c>
       <c r="L3" t="n">
         <v>5.411764705882353</v>
       </c>
       <c r="M3" t="n">
-        <v>9.110615924121603</v>
+        <v>9.11061633663415</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -605,28 +605,28 @@
         <v>64.70588235294117</v>
       </c>
       <c r="F4" t="n">
-        <v>86.70360734698583</v>
+        <v>86.70357713726115</v>
       </c>
       <c r="G4" t="n">
         <v>17</v>
       </c>
       <c r="H4" t="n">
-        <v>5.10021219688152</v>
+        <v>5.100210419838891</v>
       </c>
       <c r="I4" t="n">
-        <v>867036.0734698584</v>
+        <v>867035.7713726114</v>
       </c>
       <c r="J4" t="n">
-        <v>1867036.073469858</v>
+        <v>1867035.771372611</v>
       </c>
       <c r="K4" t="n">
-        <v>43326.29027495484</v>
+        <v>43326.28461176829</v>
       </c>
       <c r="L4" t="n">
         <v>5.411764705882353</v>
       </c>
       <c r="M4" t="n">
-        <v>9.110615924121603</v>
+        <v>9.11061633663415</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -653,28 +653,28 @@
         <v>64.70588235294117</v>
       </c>
       <c r="F5" t="n">
-        <v>86.70360734698583</v>
+        <v>86.70357713726115</v>
       </c>
       <c r="G5" t="n">
         <v>17</v>
       </c>
       <c r="H5" t="n">
-        <v>5.10021219688152</v>
+        <v>5.100210419838891</v>
       </c>
       <c r="I5" t="n">
-        <v>867036.0734698584</v>
+        <v>867035.7713726114</v>
       </c>
       <c r="J5" t="n">
-        <v>1867036.073469858</v>
+        <v>1867035.771372611</v>
       </c>
       <c r="K5" t="n">
-        <v>43326.29027495484</v>
+        <v>43326.28461176829</v>
       </c>
       <c r="L5" t="n">
         <v>5.411764705882353</v>
       </c>
       <c r="M5" t="n">
-        <v>9.110615924121603</v>
+        <v>9.11061633663415</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -701,28 +701,28 @@
         <v>61.11111111111111</v>
       </c>
       <c r="F6" t="n">
-        <v>82.23134730257878</v>
+        <v>82.23130770833332</v>
       </c>
       <c r="G6" t="n">
         <v>18</v>
       </c>
       <c r="H6" t="n">
-        <v>4.568408183476599</v>
+        <v>4.568405983796295</v>
       </c>
       <c r="I6" t="n">
-        <v>822313.4730257879</v>
+        <v>822313.0770833332</v>
       </c>
       <c r="J6" t="n">
-        <v>1822313.473025788</v>
+        <v>1822313.077083333</v>
       </c>
       <c r="K6" t="n">
-        <v>44247.8290646036</v>
+        <v>44247.82136141651</v>
       </c>
       <c r="L6" t="n">
         <v>5.777777777777778</v>
       </c>
       <c r="M6" t="n">
-        <v>9.861897909029588</v>
+        <v>9.861907471888033</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -749,28 +749,28 @@
         <v>61.11111111111111</v>
       </c>
       <c r="F7" t="n">
-        <v>82.23134730257878</v>
+        <v>82.23130770833332</v>
       </c>
       <c r="G7" t="n">
         <v>18</v>
       </c>
       <c r="H7" t="n">
-        <v>4.568408183476599</v>
+        <v>4.568405983796295</v>
       </c>
       <c r="I7" t="n">
-        <v>822313.4730257879</v>
+        <v>822313.0770833332</v>
       </c>
       <c r="J7" t="n">
-        <v>1822313.473025788</v>
+        <v>1822313.077083333</v>
       </c>
       <c r="K7" t="n">
-        <v>44247.8290646036</v>
+        <v>44247.82136141651</v>
       </c>
       <c r="L7" t="n">
         <v>5.777777777777778</v>
       </c>
       <c r="M7" t="n">
-        <v>9.861897909029588</v>
+        <v>9.861907471888033</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -797,28 +797,28 @@
         <v>66.66666666666666</v>
       </c>
       <c r="F8" t="n">
-        <v>81.03653641052605</v>
+        <v>81.0365284434739</v>
       </c>
       <c r="G8" t="n">
         <v>15</v>
       </c>
       <c r="H8" t="n">
-        <v>5.402435760701737</v>
+        <v>5.402435229564927</v>
       </c>
       <c r="I8" t="n">
-        <v>810365.3641052605</v>
+        <v>810365.284434739</v>
       </c>
       <c r="J8" t="n">
-        <v>1810365.36410526</v>
+        <v>1810365.284434739</v>
       </c>
       <c r="K8" t="n">
-        <v>38249.26677964552</v>
+        <v>38249.2657261015</v>
       </c>
       <c r="L8" t="n">
         <v>5.266666666666667</v>
       </c>
       <c r="M8" t="n">
-        <v>8.783280702976766</v>
+        <v>8.783280858880888</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -845,28 +845,28 @@
         <v>66.66666666666666</v>
       </c>
       <c r="F9" t="n">
-        <v>81.03653641052605</v>
+        <v>81.0365284434739</v>
       </c>
       <c r="G9" t="n">
         <v>15</v>
       </c>
       <c r="H9" t="n">
-        <v>5.402435760701737</v>
+        <v>5.402435229564927</v>
       </c>
       <c r="I9" t="n">
-        <v>810365.3641052605</v>
+        <v>810365.284434739</v>
       </c>
       <c r="J9" t="n">
-        <v>1810365.36410526</v>
+        <v>1810365.284434739</v>
       </c>
       <c r="K9" t="n">
-        <v>38249.26677964552</v>
+        <v>38249.2657261015</v>
       </c>
       <c r="L9" t="n">
         <v>5.266666666666667</v>
       </c>
       <c r="M9" t="n">
-        <v>8.783280702976766</v>
+        <v>8.783280858880888</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -893,28 +893,28 @@
         <v>66.66666666666666</v>
       </c>
       <c r="F10" t="n">
-        <v>81.03653641052605</v>
+        <v>81.0365284434739</v>
       </c>
       <c r="G10" t="n">
         <v>15</v>
       </c>
       <c r="H10" t="n">
-        <v>5.402435760701737</v>
+        <v>5.402435229564927</v>
       </c>
       <c r="I10" t="n">
-        <v>810365.3641052605</v>
+        <v>810365.284434739</v>
       </c>
       <c r="J10" t="n">
-        <v>1810365.36410526</v>
+        <v>1810365.284434739</v>
       </c>
       <c r="K10" t="n">
-        <v>38249.26677964552</v>
+        <v>38249.2657261015</v>
       </c>
       <c r="L10" t="n">
         <v>5.266666666666667</v>
       </c>
       <c r="M10" t="n">
-        <v>8.783280702976766</v>
+        <v>8.783280858880888</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -941,28 +941,28 @@
         <v>54.54545454545454</v>
       </c>
       <c r="F11" t="n">
-        <v>73.19692288381781</v>
+        <v>73.19692632363811</v>
       </c>
       <c r="G11" t="n">
         <v>22</v>
       </c>
       <c r="H11" t="n">
-        <v>3.327132858355355</v>
+        <v>3.327133014710823</v>
       </c>
       <c r="I11" t="n">
-        <v>731969.2288381781</v>
+        <v>731969.2632363811</v>
       </c>
       <c r="J11" t="n">
-        <v>1731969.228838178</v>
+        <v>1731969.263236381</v>
       </c>
       <c r="K11" t="n">
-        <v>50352.77841280588</v>
+        <v>50352.77975865926</v>
       </c>
       <c r="L11" t="n">
         <v>5.272727272727272</v>
       </c>
       <c r="M11" t="n">
-        <v>17.43472530400955</v>
+        <v>17.43472003067039</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -989,28 +989,28 @@
         <v>54.54545454545454</v>
       </c>
       <c r="F12" t="n">
-        <v>71.55984134044672</v>
+        <v>71.55984474775337</v>
       </c>
       <c r="G12" t="n">
         <v>22</v>
       </c>
       <c r="H12" t="n">
-        <v>3.252720060929397</v>
+        <v>3.252720215806971</v>
       </c>
       <c r="I12" t="n">
-        <v>715598.4134044673</v>
+        <v>715598.4474775337</v>
       </c>
       <c r="J12" t="n">
-        <v>1715598.413404467</v>
+        <v>1715598.447477534</v>
       </c>
       <c r="K12" t="n">
-        <v>49940.57061662957</v>
+        <v>49940.57194975188</v>
       </c>
       <c r="L12" t="n">
         <v>5.318181818181818</v>
       </c>
       <c r="M12" t="n">
-        <v>17.43472530400955</v>
+        <v>17.43472003067039</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -1037,28 +1037,28 @@
         <v>55.55555555555556</v>
       </c>
       <c r="F13" t="n">
-        <v>60.14545029242448</v>
+        <v>60.14542625472639</v>
       </c>
       <c r="G13" t="n">
         <v>18</v>
       </c>
       <c r="H13" t="n">
-        <v>3.341413905134694</v>
+        <v>3.341412569707022</v>
       </c>
       <c r="I13" t="n">
-        <v>601454.5029242449</v>
+        <v>601454.2625472639</v>
       </c>
       <c r="J13" t="n">
-        <v>1601454.502924245</v>
+        <v>1601454.262547264</v>
       </c>
       <c r="K13" t="n">
-        <v>39461.89747317667</v>
+        <v>39461.8930350616</v>
       </c>
       <c r="L13" t="n">
         <v>5.333333333333333</v>
       </c>
       <c r="M13" t="n">
-        <v>19.41862913259938</v>
+        <v>19.41863781929942</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -1085,28 +1085,28 @@
         <v>55.55555555555556</v>
       </c>
       <c r="F14" t="n">
-        <v>60.14545029242448</v>
+        <v>60.14542625472639</v>
       </c>
       <c r="G14" t="n">
         <v>18</v>
       </c>
       <c r="H14" t="n">
-        <v>3.341413905134694</v>
+        <v>3.341412569707022</v>
       </c>
       <c r="I14" t="n">
-        <v>601454.5029242449</v>
+        <v>601454.2625472639</v>
       </c>
       <c r="J14" t="n">
-        <v>1601454.502924245</v>
+        <v>1601454.262547264</v>
       </c>
       <c r="K14" t="n">
-        <v>39461.89747317667</v>
+        <v>39461.8930350616</v>
       </c>
       <c r="L14" t="n">
         <v>5.333333333333333</v>
       </c>
       <c r="M14" t="n">
-        <v>19.41862913259938</v>
+        <v>19.41863781929942</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -1133,28 +1133,28 @@
         <v>55.55555555555556</v>
       </c>
       <c r="F15" t="n">
-        <v>58.63170627346831</v>
+        <v>58.63168246298179</v>
       </c>
       <c r="G15" t="n">
         <v>18</v>
       </c>
       <c r="H15" t="n">
-        <v>3.257317015192684</v>
+        <v>3.257315692387877</v>
       </c>
       <c r="I15" t="n">
-        <v>586317.062734683</v>
+        <v>586316.8246298179</v>
       </c>
       <c r="J15" t="n">
-        <v>1586317.062734683</v>
+        <v>1586316.824629818</v>
       </c>
       <c r="K15" t="n">
-        <v>39133.87478438458</v>
+        <v>39133.87038824206</v>
       </c>
       <c r="L15" t="n">
         <v>5.388888888888889</v>
       </c>
       <c r="M15" t="n">
-        <v>20.18030901777307</v>
+        <v>20.18031762236377</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -1181,28 +1181,28 @@
         <v>55.55555555555556</v>
       </c>
       <c r="F16" t="n">
-        <v>58.63170627346831</v>
+        <v>58.63168246298179</v>
       </c>
       <c r="G16" t="n">
         <v>18</v>
       </c>
       <c r="H16" t="n">
-        <v>3.257317015192684</v>
+        <v>3.257315692387877</v>
       </c>
       <c r="I16" t="n">
-        <v>586317.062734683</v>
+        <v>586316.8246298179</v>
       </c>
       <c r="J16" t="n">
-        <v>1586317.062734683</v>
+        <v>1586316.824629818</v>
       </c>
       <c r="K16" t="n">
-        <v>39133.87478438458</v>
+        <v>39133.87038824206</v>
       </c>
       <c r="L16" t="n">
         <v>5.388888888888889</v>
       </c>
       <c r="M16" t="n">
-        <v>20.18030901777307</v>
+        <v>20.18031762236377</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1229,28 +1229,28 @@
         <v>45.45454545454545</v>
       </c>
       <c r="F17" t="n">
-        <v>23.75528123084796</v>
+        <v>23.75527171333977</v>
       </c>
       <c r="G17" t="n">
         <v>11</v>
       </c>
       <c r="H17" t="n">
-        <v>2.159571020986178</v>
+        <v>2.159570155758161</v>
       </c>
       <c r="I17" t="n">
-        <v>237552.8123084796</v>
+        <v>237552.7171333977</v>
       </c>
       <c r="J17" t="n">
-        <v>1237552.81230848</v>
+        <v>1237552.717133398</v>
       </c>
       <c r="K17" t="n">
-        <v>21200.18926792442</v>
+        <v>21200.18831088788</v>
       </c>
       <c r="L17" t="n">
         <v>5.818181818181818</v>
       </c>
       <c r="M17" t="n">
-        <v>18.06337496523121</v>
+        <v>18.06337306468325</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -1277,28 +1277,28 @@
         <v>45.45454545454545</v>
       </c>
       <c r="F18" t="n">
-        <v>23.75528123084796</v>
+        <v>23.75527171333977</v>
       </c>
       <c r="G18" t="n">
         <v>11</v>
       </c>
       <c r="H18" t="n">
-        <v>2.159571020986178</v>
+        <v>2.159570155758161</v>
       </c>
       <c r="I18" t="n">
-        <v>237552.8123084796</v>
+        <v>237552.7171333977</v>
       </c>
       <c r="J18" t="n">
-        <v>1237552.81230848</v>
+        <v>1237552.717133398</v>
       </c>
       <c r="K18" t="n">
-        <v>21200.18926792442</v>
+        <v>21200.18831088788</v>
       </c>
       <c r="L18" t="n">
         <v>5.818181818181818</v>
       </c>
       <c r="M18" t="n">
-        <v>18.06337496523121</v>
+        <v>18.06337306468325</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -1325,28 +1325,28 @@
         <v>45.45454545454545</v>
       </c>
       <c r="F19" t="n">
-        <v>23.75528123084796</v>
+        <v>23.75527171333977</v>
       </c>
       <c r="G19" t="n">
         <v>11</v>
       </c>
       <c r="H19" t="n">
-        <v>2.159571020986178</v>
+        <v>2.159570155758161</v>
       </c>
       <c r="I19" t="n">
-        <v>237552.8123084796</v>
+        <v>237552.7171333977</v>
       </c>
       <c r="J19" t="n">
-        <v>1237552.81230848</v>
+        <v>1237552.717133398</v>
       </c>
       <c r="K19" t="n">
-        <v>21200.18926792442</v>
+        <v>21200.18831088788</v>
       </c>
       <c r="L19" t="n">
         <v>5.818181818181818</v>
       </c>
       <c r="M19" t="n">
-        <v>18.06337496523121</v>
+        <v>18.06337306468325</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -1373,28 +1373,28 @@
         <v>40</v>
       </c>
       <c r="F20" t="n">
-        <v>20.34523346371006</v>
+        <v>20.34523431649685</v>
       </c>
       <c r="G20" t="n">
         <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>2.034523346371006</v>
+        <v>2.034523431649685</v>
       </c>
       <c r="I20" t="n">
-        <v>203452.3346371006</v>
+        <v>203452.3431649685</v>
       </c>
       <c r="J20" t="n">
-        <v>1203452.334637101</v>
+        <v>1203452.343164969</v>
       </c>
       <c r="K20" t="n">
-        <v>18860.65492349565</v>
+        <v>18860.65533899896</v>
       </c>
       <c r="L20" t="n">
         <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>20.32111946282102</v>
+        <v>20.32111092224943</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -1421,28 +1421,28 @@
         <v>40</v>
       </c>
       <c r="F21" t="n">
-        <v>20.34523346371006</v>
+        <v>20.34523431649685</v>
       </c>
       <c r="G21" t="n">
         <v>10</v>
       </c>
       <c r="H21" t="n">
-        <v>2.034523346371006</v>
+        <v>2.034523431649685</v>
       </c>
       <c r="I21" t="n">
-        <v>203452.3346371006</v>
+        <v>203452.3431649685</v>
       </c>
       <c r="J21" t="n">
-        <v>1203452.334637101</v>
+        <v>1203452.343164969</v>
       </c>
       <c r="K21" t="n">
-        <v>18860.65492349565</v>
+        <v>18860.65533899896</v>
       </c>
       <c r="L21" t="n">
         <v>6</v>
       </c>
       <c r="M21" t="n">
-        <v>20.32111946282102</v>
+        <v>20.32111092224943</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -1469,28 +1469,28 @@
         <v>41.66666666666667</v>
       </c>
       <c r="F22" t="n">
-        <v>17.14019683743864</v>
+        <v>17.14020444561227</v>
       </c>
       <c r="G22" t="n">
         <v>12</v>
       </c>
       <c r="H22" t="n">
-        <v>1.42834973645322</v>
+        <v>1.428350370467689</v>
       </c>
       <c r="I22" t="n">
-        <v>171401.9683743864</v>
+        <v>171402.0444561227</v>
       </c>
       <c r="J22" t="n">
-        <v>1171401.968374386</v>
+        <v>1171402.044456123</v>
       </c>
       <c r="K22" t="n">
-        <v>21964.92599062613</v>
+        <v>21964.92823664171</v>
       </c>
       <c r="L22" t="n">
         <v>6.166666666666667</v>
       </c>
       <c r="M22" t="n">
-        <v>22.44312897754746</v>
+        <v>22.44311617674489</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -1517,28 +1517,28 @@
         <v>41.66666666666667</v>
       </c>
       <c r="F23" t="n">
-        <v>17.14019683743864</v>
+        <v>17.14020444561227</v>
       </c>
       <c r="G23" t="n">
         <v>12</v>
       </c>
       <c r="H23" t="n">
-        <v>1.42834973645322</v>
+        <v>1.428350370467689</v>
       </c>
       <c r="I23" t="n">
-        <v>171401.9683743864</v>
+        <v>171402.0444561227</v>
       </c>
       <c r="J23" t="n">
-        <v>1171401.968374386</v>
+        <v>1171402.044456123</v>
       </c>
       <c r="K23" t="n">
-        <v>21964.92599062613</v>
+        <v>21964.92823664171</v>
       </c>
       <c r="L23" t="n">
         <v>6.166666666666667</v>
       </c>
       <c r="M23" t="n">
-        <v>22.44312897754746</v>
+        <v>22.44311617674489</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -1565,28 +1565,28 @@
         <v>40</v>
       </c>
       <c r="F24" t="n">
-        <v>16.495973625494</v>
+        <v>16.49597445100425</v>
       </c>
       <c r="G24" t="n">
         <v>10</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6495973625494</v>
+        <v>1.649597445100425</v>
       </c>
       <c r="I24" t="n">
-        <v>164959.73625494</v>
+        <v>164959.7445100425</v>
       </c>
       <c r="J24" t="n">
-        <v>1164959.73625494</v>
+        <v>1164959.744510042</v>
       </c>
       <c r="K24" t="n">
-        <v>18409.61063794609</v>
+        <v>18409.61104023447</v>
       </c>
       <c r="L24" t="n">
         <v>4.4</v>
       </c>
       <c r="M24" t="n">
-        <v>22.86966007368175</v>
+        <v>22.86965180628158</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -1613,28 +1613,28 @@
         <v>40</v>
       </c>
       <c r="F25" t="n">
-        <v>16.495973625494</v>
+        <v>16.49597445100425</v>
       </c>
       <c r="G25" t="n">
         <v>10</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6495973625494</v>
+        <v>1.649597445100425</v>
       </c>
       <c r="I25" t="n">
-        <v>164959.73625494</v>
+        <v>164959.7445100425</v>
       </c>
       <c r="J25" t="n">
-        <v>1164959.73625494</v>
+        <v>1164959.744510042</v>
       </c>
       <c r="K25" t="n">
-        <v>18409.61063794609</v>
+        <v>18409.61104023447</v>
       </c>
       <c r="L25" t="n">
         <v>4.4</v>
       </c>
       <c r="M25" t="n">
-        <v>22.86966007368175</v>
+        <v>22.86965180628158</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -1661,28 +1661,28 @@
         <v>40</v>
       </c>
       <c r="F26" t="n">
-        <v>16.495973625494</v>
+        <v>16.49597445100425</v>
       </c>
       <c r="G26" t="n">
         <v>10</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6495973625494</v>
+        <v>1.649597445100425</v>
       </c>
       <c r="I26" t="n">
-        <v>164959.73625494</v>
+        <v>164959.7445100425</v>
       </c>
       <c r="J26" t="n">
-        <v>1164959.73625494</v>
+        <v>1164959.744510042</v>
       </c>
       <c r="K26" t="n">
-        <v>18409.61063794609</v>
+        <v>18409.61104023447</v>
       </c>
       <c r="L26" t="n">
         <v>4.4</v>
       </c>
       <c r="M26" t="n">
-        <v>22.86966007368175</v>
+        <v>22.86965180628158</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -1709,28 +1709,28 @@
         <v>40</v>
       </c>
       <c r="F27" t="n">
-        <v>16.4565122289249</v>
+        <v>16.45651305415554</v>
       </c>
       <c r="G27" t="n">
         <v>10</v>
       </c>
       <c r="H27" t="n">
-        <v>1.64565122289249</v>
+        <v>1.645651305415554</v>
       </c>
       <c r="I27" t="n">
-        <v>164565.122289249</v>
+        <v>164565.1305415554</v>
       </c>
       <c r="J27" t="n">
-        <v>1164565.122289249</v>
+        <v>1164565.130541555</v>
       </c>
       <c r="K27" t="n">
-        <v>18404.98667433481</v>
+        <v>18404.98707648772</v>
       </c>
       <c r="L27" t="n">
         <v>7.4</v>
       </c>
       <c r="M27" t="n">
-        <v>22.89578690739641</v>
+        <v>22.89577864279671</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -1757,28 +1757,28 @@
         <v>38.46153846153847</v>
       </c>
       <c r="F28" t="n">
-        <v>16.12986652932521</v>
+        <v>16.12987990238187</v>
       </c>
       <c r="G28" t="n">
         <v>13</v>
       </c>
       <c r="H28" t="n">
-        <v>1.240758963794247</v>
+        <v>1.240759992490913</v>
       </c>
       <c r="I28" t="n">
-        <v>161298.6652932521</v>
+        <v>161298.7990238187</v>
       </c>
       <c r="J28" t="n">
-        <v>1161298.665293252</v>
+        <v>1161298.799023819</v>
       </c>
       <c r="K28" t="n">
-        <v>23858.97238095295</v>
+        <v>23858.974442844</v>
       </c>
       <c r="L28" t="n">
         <v>4.538461538461538</v>
       </c>
       <c r="M28" t="n">
-        <v>23.11205441486057</v>
+        <v>23.11203786417014</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -1805,28 +1805,28 @@
         <v>38.46153846153847</v>
       </c>
       <c r="F29" t="n">
-        <v>16.12986652932521</v>
+        <v>16.12987990238187</v>
       </c>
       <c r="G29" t="n">
         <v>13</v>
       </c>
       <c r="H29" t="n">
-        <v>1.240758963794247</v>
+        <v>1.240759992490913</v>
       </c>
       <c r="I29" t="n">
-        <v>161298.6652932521</v>
+        <v>161298.7990238187</v>
       </c>
       <c r="J29" t="n">
-        <v>1161298.665293252</v>
+        <v>1161298.799023819</v>
       </c>
       <c r="K29" t="n">
-        <v>23858.97238095295</v>
+        <v>23858.974442844</v>
       </c>
       <c r="L29" t="n">
         <v>4.538461538461538</v>
       </c>
       <c r="M29" t="n">
-        <v>23.11205441486057</v>
+        <v>23.11203786417014</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -1853,28 +1853,28 @@
         <v>38.46153846153847</v>
       </c>
       <c r="F30" t="n">
-        <v>16.12986652932521</v>
+        <v>16.12987990238187</v>
       </c>
       <c r="G30" t="n">
         <v>13</v>
       </c>
       <c r="H30" t="n">
-        <v>1.240758963794247</v>
+        <v>1.240759992490913</v>
       </c>
       <c r="I30" t="n">
-        <v>161298.6652932521</v>
+        <v>161298.7990238187</v>
       </c>
       <c r="J30" t="n">
-        <v>1161298.665293252</v>
+        <v>1161298.799023819</v>
       </c>
       <c r="K30" t="n">
-        <v>23858.97238095295</v>
+        <v>23858.974442844</v>
       </c>
       <c r="L30" t="n">
         <v>4.538461538461538</v>
       </c>
       <c r="M30" t="n">
-        <v>23.11205441486057</v>
+        <v>23.11203786417014</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -1901,28 +1901,28 @@
         <v>41.66666666666667</v>
       </c>
       <c r="F31" t="n">
-        <v>13.35504010311707</v>
+        <v>13.35504746544738</v>
       </c>
       <c r="G31" t="n">
         <v>12</v>
       </c>
       <c r="H31" t="n">
-        <v>1.112920008593089</v>
+        <v>1.112920622120615</v>
       </c>
       <c r="I31" t="n">
-        <v>133550.4010311707</v>
+        <v>133550.4746544738</v>
       </c>
       <c r="J31" t="n">
-        <v>1133550.401031171</v>
+        <v>1133550.474654474</v>
       </c>
       <c r="K31" t="n">
-        <v>21405.91909900709</v>
+        <v>21405.92129330409</v>
       </c>
       <c r="L31" t="n">
         <v>7.333333333333333</v>
       </c>
       <c r="M31" t="n">
-        <v>24.94922782806363</v>
+        <v>24.94921544089402</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -1949,28 +1949,28 @@
         <v>30</v>
       </c>
       <c r="F32" t="n">
-        <v>-9.380418605275139</v>
+        <v>-9.380365888848493</v>
       </c>
       <c r="G32" t="n">
         <v>10</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.9380418605275139</v>
+        <v>-0.9380365888848493</v>
       </c>
       <c r="I32" t="n">
-        <v>-93804.18605275138</v>
+        <v>-93803.65888848493</v>
       </c>
       <c r="J32" t="n">
-        <v>906195.8139472486</v>
+        <v>906196.3411115151</v>
       </c>
       <c r="K32" t="n">
-        <v>18087.70385511089</v>
+        <v>18087.71195303221</v>
       </c>
       <c r="L32" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>23.00449062451491</v>
+        <v>23.00448223996911</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -1997,28 +1997,28 @@
         <v>30</v>
       </c>
       <c r="F33" t="n">
-        <v>-9.380418605275139</v>
+        <v>-9.380365888848493</v>
       </c>
       <c r="G33" t="n">
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9380418605275139</v>
+        <v>-0.9380365888848493</v>
       </c>
       <c r="I33" t="n">
-        <v>-93804.18605275138</v>
+        <v>-93803.65888848493</v>
       </c>
       <c r="J33" t="n">
-        <v>906195.8139472486</v>
+        <v>906196.3411115151</v>
       </c>
       <c r="K33" t="n">
-        <v>18087.70385511089</v>
+        <v>18087.71195303221</v>
       </c>
       <c r="L33" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>23.00449062451491</v>
+        <v>23.00448223996911</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -2045,28 +2045,28 @@
         <v>30</v>
       </c>
       <c r="F34" t="n">
-        <v>-9.380418605275139</v>
+        <v>-9.380365888848493</v>
       </c>
       <c r="G34" t="n">
         <v>10</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9380418605275139</v>
+        <v>-0.9380365888848493</v>
       </c>
       <c r="I34" t="n">
-        <v>-93804.18605275138</v>
+        <v>-93803.65888848493</v>
       </c>
       <c r="J34" t="n">
-        <v>906195.8139472486</v>
+        <v>906196.3411115151</v>
       </c>
       <c r="K34" t="n">
-        <v>18087.70385511089</v>
+        <v>18087.71195303221</v>
       </c>
       <c r="L34" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>23.00449062451491</v>
+        <v>23.00448223996911</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -2093,28 +2093,28 @@
         <v>22.22222222222222</v>
       </c>
       <c r="F35" t="n">
-        <v>-10.33621768878931</v>
+        <v>-10.33617678390859</v>
       </c>
       <c r="G35" t="n">
         <v>9</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.148468632087701</v>
+        <v>-1.148464087100954</v>
       </c>
       <c r="I35" t="n">
-        <v>-103362.1768878931</v>
+        <v>-103361.7678390859</v>
       </c>
       <c r="J35" t="n">
-        <v>896637.8231121069</v>
+        <v>896638.2321609141</v>
       </c>
       <c r="K35" t="n">
-        <v>15810.27362680338</v>
+        <v>15810.27962455953</v>
       </c>
       <c r="L35" t="n">
         <v>11.22222222222222</v>
       </c>
       <c r="M35" t="n">
-        <v>23.36338005122904</v>
+        <v>23.36334508937805</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -2141,28 +2141,28 @@
         <v>22.22222222222222</v>
       </c>
       <c r="F36" t="n">
-        <v>-10.33621768878931</v>
+        <v>-10.33617678390859</v>
       </c>
       <c r="G36" t="n">
         <v>9</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.148468632087701</v>
+        <v>-1.148464087100954</v>
       </c>
       <c r="I36" t="n">
-        <v>-103362.1768878931</v>
+        <v>-103361.7678390859</v>
       </c>
       <c r="J36" t="n">
-        <v>896637.8231121069</v>
+        <v>896638.2321609141</v>
       </c>
       <c r="K36" t="n">
-        <v>15810.27362680338</v>
+        <v>15810.27962455953</v>
       </c>
       <c r="L36" t="n">
         <v>11.22222222222222</v>
       </c>
       <c r="M36" t="n">
-        <v>23.36338005122904</v>
+        <v>23.36334508937805</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -2189,28 +2189,28 @@
         <v>25</v>
       </c>
       <c r="F37" t="n">
-        <v>-11.13645464472597</v>
+        <v>-11.13639548600812</v>
       </c>
       <c r="G37" t="n">
         <v>8</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.392056830590747</v>
+        <v>-1.392049435751015</v>
       </c>
       <c r="I37" t="n">
-        <v>-111364.5464472597</v>
+        <v>-111363.9548600812</v>
       </c>
       <c r="J37" t="n">
-        <v>888635.4535527403</v>
+        <v>888636.0451399188</v>
       </c>
       <c r="K37" t="n">
-        <v>14045.16168299097</v>
+        <v>14045.16865722841</v>
       </c>
       <c r="L37" t="n">
         <v>8.75</v>
       </c>
       <c r="M37" t="n">
-        <v>24.0473513703088</v>
+        <v>24.04730080670264</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -2237,28 +2237,28 @@
         <v>25</v>
       </c>
       <c r="F38" t="n">
-        <v>-11.13645464472597</v>
+        <v>-11.13639548600812</v>
       </c>
       <c r="G38" t="n">
         <v>8</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.392056830590747</v>
+        <v>-1.392049435751015</v>
       </c>
       <c r="I38" t="n">
-        <v>-111364.5464472597</v>
+        <v>-111363.9548600812</v>
       </c>
       <c r="J38" t="n">
-        <v>888635.4535527403</v>
+        <v>888636.0451399188</v>
       </c>
       <c r="K38" t="n">
-        <v>14045.16168299097</v>
+        <v>14045.16865722841</v>
       </c>
       <c r="L38" t="n">
         <v>8.75</v>
       </c>
       <c r="M38" t="n">
-        <v>24.0473513703088</v>
+        <v>24.04730080670264</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -2285,28 +2285,28 @@
         <v>25</v>
       </c>
       <c r="F39" t="n">
-        <v>-11.13645464472597</v>
+        <v>-11.13639548600812</v>
       </c>
       <c r="G39" t="n">
         <v>8</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.392056830590747</v>
+        <v>-1.392049435751015</v>
       </c>
       <c r="I39" t="n">
-        <v>-111364.5464472597</v>
+        <v>-111363.9548600812</v>
       </c>
       <c r="J39" t="n">
-        <v>888635.4535527403</v>
+        <v>888636.0451399188</v>
       </c>
       <c r="K39" t="n">
-        <v>14045.16168299097</v>
+        <v>14045.16865722841</v>
       </c>
       <c r="L39" t="n">
         <v>8.75</v>
       </c>
       <c r="M39" t="n">
-        <v>24.0473513703088</v>
+        <v>24.04730080670264</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -2333,28 +2333,28 @@
         <v>22.22222222222222</v>
       </c>
       <c r="F40" t="n">
-        <v>-13.23352773779847</v>
+        <v>-13.23348815467908</v>
       </c>
       <c r="G40" t="n">
         <v>9</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.470391970866497</v>
+        <v>-1.47038757274212</v>
       </c>
       <c r="I40" t="n">
-        <v>-132335.2773779847</v>
+        <v>-132334.8815467908</v>
       </c>
       <c r="J40" t="n">
-        <v>867664.7226220153</v>
+        <v>867665.1184532092</v>
       </c>
       <c r="K40" t="n">
-        <v>15450.5573568401</v>
+        <v>15450.56319756242</v>
       </c>
       <c r="L40" t="n">
         <v>12.77777777777778</v>
       </c>
       <c r="M40" t="n">
-        <v>25.83974278516993</v>
+        <v>25.83970895304286</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -2381,28 +2381,28 @@
         <v>12.5</v>
       </c>
       <c r="F41" t="n">
-        <v>-18.35536665277703</v>
+        <v>-18.35532125027238</v>
       </c>
       <c r="G41" t="n">
         <v>8</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.294420831597129</v>
+        <v>-2.294415156284047</v>
       </c>
       <c r="I41" t="n">
-        <v>-183553.6665277703</v>
+        <v>-183553.2125027238</v>
       </c>
       <c r="J41" t="n">
-        <v>816446.3334722297</v>
+        <v>816446.7874972762</v>
       </c>
       <c r="K41" t="n">
-        <v>13284.21522915587</v>
+        <v>13284.22078581761</v>
       </c>
       <c r="L41" t="n">
         <v>10.25</v>
       </c>
       <c r="M41" t="n">
-        <v>30.217434783525</v>
+        <v>30.2173959775054</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -2429,28 +2429,28 @@
         <v>12.5</v>
       </c>
       <c r="F42" t="n">
-        <v>-18.35536665277703</v>
+        <v>-18.35532125027238</v>
       </c>
       <c r="G42" t="n">
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.294420831597129</v>
+        <v>-2.294415156284047</v>
       </c>
       <c r="I42" t="n">
-        <v>-183553.6665277703</v>
+        <v>-183553.2125027238</v>
       </c>
       <c r="J42" t="n">
-        <v>816446.3334722297</v>
+        <v>816446.7874972762</v>
       </c>
       <c r="K42" t="n">
-        <v>13284.21522915587</v>
+        <v>13284.22078581761</v>
       </c>
       <c r="L42" t="n">
         <v>10.25</v>
       </c>
       <c r="M42" t="n">
-        <v>30.217434783525</v>
+        <v>30.2173959775054</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -2477,28 +2477,28 @@
         <v>18.18181818181818</v>
       </c>
       <c r="F43" t="n">
-        <v>-19.0250500073108</v>
+        <v>-19.02503086867675</v>
       </c>
       <c r="G43" t="n">
         <v>11</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.729550000664618</v>
+        <v>-1.729548260788795</v>
       </c>
       <c r="I43" t="n">
-        <v>-190250.500073108</v>
+        <v>-190250.3086867675</v>
       </c>
       <c r="J43" t="n">
-        <v>809749.499926892</v>
+        <v>809749.6913132325</v>
       </c>
       <c r="K43" t="n">
-        <v>18083.65169675799</v>
+        <v>18083.65532772358</v>
       </c>
       <c r="L43" t="n">
         <v>7.363636363636363</v>
       </c>
       <c r="M43" t="n">
-        <v>30.78982050498932</v>
+        <v>30.7898041469885</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -2525,28 +2525,28 @@
         <v>18.18181818181818</v>
       </c>
       <c r="F44" t="n">
-        <v>-19.0250500073108</v>
+        <v>-19.02503086867675</v>
       </c>
       <c r="G44" t="n">
         <v>11</v>
       </c>
       <c r="H44" t="n">
-        <v>-1.729550000664618</v>
+        <v>-1.729548260788795</v>
       </c>
       <c r="I44" t="n">
-        <v>-190250.500073108</v>
+        <v>-190250.3086867675</v>
       </c>
       <c r="J44" t="n">
-        <v>809749.499926892</v>
+        <v>809749.6913132325</v>
       </c>
       <c r="K44" t="n">
-        <v>18083.65169675799</v>
+        <v>18083.65532772358</v>
       </c>
       <c r="L44" t="n">
         <v>7.363636363636363</v>
       </c>
       <c r="M44" t="n">
-        <v>30.78982050498932</v>
+        <v>30.7898041469885</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -2573,28 +2573,28 @@
         <v>18.18181818181818</v>
       </c>
       <c r="F45" t="n">
-        <v>-19.0250500073108</v>
+        <v>-19.02503086867675</v>
       </c>
       <c r="G45" t="n">
         <v>11</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.729550000664618</v>
+        <v>-1.729548260788795</v>
       </c>
       <c r="I45" t="n">
-        <v>-190250.500073108</v>
+        <v>-190250.3086867675</v>
       </c>
       <c r="J45" t="n">
-        <v>809749.499926892</v>
+        <v>809749.6913132325</v>
       </c>
       <c r="K45" t="n">
-        <v>18083.65169675799</v>
+        <v>18083.65532772358</v>
       </c>
       <c r="L45" t="n">
         <v>7.363636363636363</v>
       </c>
       <c r="M45" t="n">
-        <v>30.78982050498932</v>
+        <v>30.7898041469885</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -2621,28 +2621,28 @@
         <v>12.5</v>
       </c>
       <c r="F46" t="n">
-        <v>-20.99355356110469</v>
+        <v>-20.99350962569335</v>
       </c>
       <c r="G46" t="n">
         <v>8</v>
       </c>
       <c r="H46" t="n">
-        <v>-2.624194195138087</v>
+        <v>-2.624188703211669</v>
       </c>
       <c r="I46" t="n">
-        <v>-209935.5356110469</v>
+        <v>-209935.0962569335</v>
       </c>
       <c r="J46" t="n">
-        <v>790064.4643889531</v>
+        <v>790064.9037430665</v>
       </c>
       <c r="K46" t="n">
-        <v>13006.12360396261</v>
+        <v>13006.12901784361</v>
       </c>
       <c r="L46" t="n">
         <v>12</v>
       </c>
       <c r="M46" t="n">
-        <v>32.4723221219331</v>
+        <v>32.47228456985427</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
